--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_middellaag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_middellaag.xlsx
@@ -406,22 +406,22 @@
         <v>1157</v>
       </c>
       <c r="C2">
-        <v>981</v>
+        <v>1072</v>
       </c>
       <c r="D2">
         <v>606</v>
       </c>
       <c r="E2">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F2">
         <v>1166</v>
       </c>
       <c r="G2">
-        <v>1158</v>
+        <v>1194</v>
       </c>
       <c r="H2">
-        <v>1295</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -432,22 +432,22 @@
         <v>1208</v>
       </c>
       <c r="C3">
-        <v>1002</v>
+        <v>1097</v>
       </c>
       <c r="D3">
         <v>577</v>
       </c>
       <c r="E3">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="F3">
         <v>1213</v>
       </c>
       <c r="G3">
-        <v>1167</v>
+        <v>1215</v>
       </c>
       <c r="H3">
-        <v>1318</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -458,22 +458,22 @@
         <v>1064</v>
       </c>
       <c r="C4">
-        <v>1039</v>
+        <v>1056</v>
       </c>
       <c r="D4">
         <v>347</v>
       </c>
       <c r="E4">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="F4">
         <v>1073</v>
       </c>
       <c r="G4">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="H4">
-        <v>1261</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -484,7 +484,7 @@
         <v>1281</v>
       </c>
       <c r="C5">
-        <v>1132</v>
+        <v>1202</v>
       </c>
       <c r="D5">
         <v>219</v>
@@ -496,7 +496,7 @@
         <v>1282</v>
       </c>
       <c r="G5">
-        <v>1177</v>
+        <v>1238</v>
       </c>
       <c r="H5">
         <v>1357</v>
@@ -510,7 +510,7 @@
         <v>1262</v>
       </c>
       <c r="C6">
-        <v>1123</v>
+        <v>1175</v>
       </c>
       <c r="D6">
         <v>99</v>
@@ -522,7 +522,7 @@
         <v>1264</v>
       </c>
       <c r="G6">
-        <v>1141</v>
+        <v>1193</v>
       </c>
       <c r="H6">
         <v>1349</v>
@@ -536,7 +536,7 @@
         <v>1305</v>
       </c>
       <c r="C7">
-        <v>1177</v>
+        <v>1212</v>
       </c>
       <c r="D7">
         <v>187</v>
@@ -548,7 +548,7 @@
         <v>1306</v>
       </c>
       <c r="G7">
-        <v>1208</v>
+        <v>1243</v>
       </c>
       <c r="H7">
         <v>1365</v>
@@ -562,22 +562,22 @@
         <v>1187</v>
       </c>
       <c r="C8">
-        <v>722</v>
+        <v>914</v>
       </c>
       <c r="D8">
         <v>199</v>
       </c>
       <c r="E8">
-        <v>1251</v>
+        <v>1262</v>
       </c>
       <c r="F8">
         <v>1187</v>
       </c>
       <c r="G8">
-        <v>807</v>
+        <v>967</v>
       </c>
       <c r="H8">
-        <v>1251</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -588,22 +588,22 @@
         <v>1317</v>
       </c>
       <c r="C9">
-        <v>1065</v>
+        <v>1177</v>
       </c>
       <c r="D9">
         <v>289</v>
       </c>
       <c r="E9">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="F9">
         <v>1318</v>
       </c>
       <c r="G9">
-        <v>1119</v>
+        <v>1230</v>
       </c>
       <c r="H9">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -614,7 +614,7 @@
         <v>1316</v>
       </c>
       <c r="C10">
-        <v>1158</v>
+        <v>1211</v>
       </c>
       <c r="D10">
         <v>468</v>
@@ -626,7 +626,7 @@
         <v>1319</v>
       </c>
       <c r="G10">
-        <v>1256</v>
+        <v>1286</v>
       </c>
       <c r="H10">
         <v>1366</v>
@@ -640,7 +640,7 @@
         <v>1303</v>
       </c>
       <c r="C11">
-        <v>1161</v>
+        <v>1209</v>
       </c>
       <c r="D11">
         <v>403</v>
@@ -652,7 +652,7 @@
         <v>1305</v>
       </c>
       <c r="G11">
-        <v>1249</v>
+        <v>1273</v>
       </c>
       <c r="H11">
         <v>1367</v>
@@ -666,7 +666,7 @@
         <v>1157</v>
       </c>
       <c r="C12">
-        <v>1172</v>
+        <v>1235</v>
       </c>
       <c r="D12">
         <v>113</v>
@@ -678,7 +678,7 @@
         <v>1162</v>
       </c>
       <c r="G12">
-        <v>1193</v>
+        <v>1256</v>
       </c>
       <c r="H12">
         <v>1345</v>
@@ -692,7 +692,7 @@
         <v>1308</v>
       </c>
       <c r="C13">
-        <v>1156</v>
+        <v>1204</v>
       </c>
       <c r="D13">
         <v>362</v>
@@ -704,7 +704,7 @@
         <v>1311</v>
       </c>
       <c r="G13">
-        <v>1238</v>
+        <v>1263</v>
       </c>
       <c r="H13">
         <v>1364</v>
